--- a/ig/ch-vacd/StructureDefinition-ch-vacd-laboratory-serology.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-laboratory-serology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>Verification Status</t>
   </si>
   <si>
-    <t>Status of verification by a practitioner</t>
+    <t>Status of verification by a practitioner. Attention: changes the interpretation of the content of the resource!</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -940,7 +940,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
+    <t>Quantity {http://fhir.ch/ig/ch-core/StructureDefinition/ch-core-quantity-with-emed-units}
 CodeableConcept</t>
   </si>
   <si>
